--- a/4_results_excel/summary_comparison_sample_size.xlsx
+++ b/4_results_excel/summary_comparison_sample_size.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Battuto\Desktop\malenia\supplementary_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadik\My Drive\Operation\ocean\Prall_etal.DiscretePrediction.CommunicationsBiology\4_results_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACDFD93-574D-4E51-98E4-B1E59945858B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594CD61C-CC54-474D-980C-8922F6C9D19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
@@ -917,19 +917,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68053A4E-B426-4D02-A5F1-14665BC27170}">
   <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="110" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>55</v>
       </c>
       <c r="B1" s="20"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -937,7 +937,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -945,72 +945,72 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1034,13 +1034,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>65</v>
       </c>
       <c r="B21" s="20"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -1056,72 +1056,72 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>59</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>61</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
@@ -1145,22 +1145,22 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B41" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B42" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>62</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>63</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>64</v>
       </c>
@@ -1184,17 +1184,17 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B47" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B48" s="8" t="s">
         <v>31</v>
       </c>
@@ -1211,28 +1211,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A74C9B-4AE5-4EE5-B762-F97942C73527}">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.1796875" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.1796875" customWidth="1"/>
-    <col min="13" max="13" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.21875" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.21875" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>54</v>
       </c>
@@ -1255,7 +1255,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>5.9020766522400597E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>5.9769158007097867E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>6.3333139881252276E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>5.9979981238657713E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>5.9807561957611374E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>6.0198184817072571E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>6.2668079372145497E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>6.6230497016806208E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>6.1854197675503153E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>6.1455048356063184E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>5.8875800795431678E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>6.2608411474277065E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>17</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>6.4244562168702807E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>77</v>
       </c>
@@ -1954,19 +1954,19 @@
         <v>6.1541953021770915E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="18">
-        <f>2*_xlfn.STDEV.S(D3:D15)/COUNT(D3:D15)</f>
-        <v>3.4021500686837298E-2</v>
+        <f>2*_xlfn.STDEV.S(D3:D15)/SQRT(COUNT(D3:D15))</f>
+        <v>0.1226662651946252</v>
       </c>
       <c r="E17" s="18">
-        <f>2*_xlfn.STDEV.S(E3:E15)/COUNT(E3:E15)</f>
-        <v>7.8337526129548709E-4</v>
+        <f>2*_xlfn.STDEV.S(E3:E15)/SQRT(COUNT(E3:E15))</f>
+        <v>2.8244996725308798E-3</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>79</v>
@@ -1974,12 +1974,12 @@
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
       <c r="J17" s="18">
-        <f>2*_xlfn.STDEV.S(J3:J15)/COUNT(J3:J15)</f>
-        <v>1.5646939713282463E-2</v>
+        <f>2*_xlfn.STDEV.S(J3:J15)/SQRT(COUNT(J3:J15))</f>
+        <v>5.6415843440333735E-2</v>
       </c>
       <c r="K17" s="18">
-        <f>2*_xlfn.STDEV.S(K3:K15)/COUNT(K3:K15)</f>
-        <v>5.7574643961355956E-4</v>
+        <f>2*_xlfn.STDEV.S(K3:K15)/SQRT(COUNT(K3:K15))</f>
+        <v>2.0758833096925205E-3</v>
       </c>
       <c r="M17" s="20" t="s">
         <v>79</v>
@@ -1987,12 +1987,12 @@
       <c r="N17" s="20"/>
       <c r="O17" s="20"/>
       <c r="P17" s="18">
-        <f>2*_xlfn.STDEV.S(P3:P15)/COUNT(P3:P15)</f>
-        <v>3.0876132006551573E-3</v>
+        <f>2*_xlfn.STDEV.S(P3:P15)/SQRT(COUNT(P3:P15))</f>
+        <v>1.1132547713761654E-2</v>
       </c>
       <c r="Q17" s="18">
-        <f>2*_xlfn.STDEV.S(Q3:Q15)/COUNT(Q3:Q15)</f>
-        <v>3.4074569322537743E-4</v>
+        <f>2*_xlfn.STDEV.S(Q3:Q15)/SQRT(COUNT(Q3:Q15))</f>
+        <v>1.2285760688176208E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2014,18 +2014,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD44F911-1668-46D7-8E1E-8B1B07959405}">
   <dimension ref="A1:J89"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="4" width="13.7265625" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="0.81640625" customWidth="1"/>
-    <col min="7" max="8" width="13.6328125" customWidth="1"/>
-    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.77734375" customWidth="1"/>
+    <col min="7" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>72</v>
       </c>
@@ -2038,7 +2038,7 @@
       <c r="H1" s="20"/>
       <c r="I1" s="20"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>1.1060947359424899E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>3.3556783528842803E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>8.2295242726830198E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>2.8399474521698002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>3.0459207484708602E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>5.2346480372209202E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>9.0407446521490707E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>3.6663984371591497E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>8.2295242726830198E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>1.20725812342692E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>2.6343975339602001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>4.0301432266049902E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>17</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>0.69114917789727204</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>60</v>
       </c>
@@ -2447,38 +2447,38 @@
         <v>3.7069674715350463E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>78</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="17">
-        <f>2*_xlfn.STDEV.S(C3:C14)/COUNT(C3:C14)</f>
-        <v>1.2757053901368616E-2</v>
+        <f>2*_xlfn.STDEV.S(C3:C14)/SQRT(COUNT(C3:C14))</f>
+        <v>4.4191731024130418E-2</v>
       </c>
       <c r="D17" s="17">
-        <f t="shared" ref="D17:I17" si="1">2*_xlfn.STDEV.S(D3:D14)/COUNT(D3:D14)</f>
-        <v>1.2620821807538646E-2</v>
+        <f t="shared" ref="D17:E17" si="1">2*_xlfn.STDEV.S(D3:D14)/SQRT(COUNT(D3:D14))</f>
+        <v>4.3719809207860422E-2</v>
       </c>
       <c r="E17" s="17">
         <f t="shared" si="1"/>
-        <v>5.2505210579971351E-3</v>
+        <v>1.8188338477322669E-2</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="17">
-        <f t="shared" si="1"/>
-        <v>2.8626119229805857E-2</v>
+        <f>2*_xlfn.STDEV.S(G3:G14)/SQRT(COUNT(G3:G14))</f>
+        <v>9.9163785859096409E-2</v>
       </c>
       <c r="H17" s="17">
-        <f t="shared" si="1"/>
-        <v>2.5721731571531663E-2</v>
+        <f t="shared" ref="H17:I17" si="2">2*_xlfn.STDEV.S(H3:H14)/SQRT(COUNT(H3:H14))</f>
+        <v>8.9102691881082607E-2</v>
       </c>
       <c r="I17" s="17">
-        <f t="shared" si="1"/>
-        <v>4.10342146539592E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>1.421466892586894E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>73</v>
       </c>
@@ -2492,7 +2492,7 @@
       <c r="I19" s="20"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>0</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>1.20725812342692E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>3.3556783528842803E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>7.6881044335957605E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>3.0459207484708602E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>6.5071996743714805E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>5.1293294387550599E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>1.20725812342692E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>3.9780870011844598E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>9.4310679471241304E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>1.6129381929883599E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>4.3951887529182797E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>0.107585210679937</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>17</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>0.69514918323061803</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="20" t="s">
         <v>60</v>
       </c>
@@ -2880,59 +2880,59 @@
         <v>0.63448512250383615</v>
       </c>
       <c r="D34" s="17">
-        <f t="shared" ref="D34:I34" si="2">AVERAGE(D21:D32)</f>
+        <f t="shared" ref="D34:I34" si="3">AVERAGE(D21:D32)</f>
         <v>0.73055225029491389</v>
       </c>
       <c r="E34" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.94764616044940952</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.55358068168162389</v>
       </c>
       <c r="H34" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.41515570802450047</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.8597126547616838E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>78</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="17">
-        <f>2*_xlfn.STDEV.S(C21:C32)/COUNT(C21:C32)</f>
-        <v>2.5401816155599163E-2</v>
+        <f>2*_xlfn.STDEV.S(C21:C32)/SQRT(COUNT(C21:C32))</f>
+        <v>8.7994472372043372E-2</v>
       </c>
       <c r="D35" s="17">
-        <f t="shared" ref="D35:I35" si="3">2*_xlfn.STDEV.S(D21:D32)/COUNT(D21:D32)</f>
-        <v>2.8607794894405542E-2</v>
+        <f t="shared" ref="D35:E35" si="4">2*_xlfn.STDEV.S(D21:D32)/SQRT(COUNT(D21:D32))</f>
+        <v>9.9100308499239856E-2</v>
       </c>
       <c r="E35" s="17">
-        <f t="shared" si="3"/>
-        <v>5.911140810223918E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.0476792428003369E-2</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="17">
-        <f t="shared" si="3"/>
-        <v>4.2421747630926536E-2</v>
+        <f>2*_xlfn.STDEV.S(G21:G32)/SQRT(COUNT(G21:G32))</f>
+        <v>0.14695324448525882</v>
       </c>
       <c r="H35" s="17">
-        <f t="shared" si="3"/>
-        <v>5.7992778543254214E-2</v>
+        <f t="shared" ref="H35:I35" si="5">2*_xlfn.STDEV.S(H21:H32)/SQRT(COUNT(H21:H32))</f>
+        <v>0.20089287781801304</v>
       </c>
       <c r="I35" s="17">
-        <f t="shared" si="3"/>
-        <v>5.2763847761362372E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v>1.8277933025101799E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
         <v>74</v>
       </c>
@@ -2945,7 +2945,7 @@
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>0</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>1.359208196407855E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>2</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>3.7182925777801495E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>8.8831810917996856E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>2.5317807984289901E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>2.0202707317519501E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>4.1343099309477049E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>2.0202707317519501E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>3.8740828316430602E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>9.65109003808437E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>2.2757117943336999E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>6.5071996743714805E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>0.12556386571206751</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>17</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>0.6921481792286085</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="20" t="s">
         <v>60</v>
       </c>
@@ -3333,59 +3333,59 @@
         <v>0.70779212280302195</v>
       </c>
       <c r="D52" s="17">
-        <f t="shared" ref="D52:I52" si="4">AVERAGE(D39:D50)</f>
+        <f t="shared" ref="D52:I52" si="6">AVERAGE(D39:D50)</f>
         <v>0.78285485482163708</v>
       </c>
       <c r="E52" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.87163191300370146</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.4338895576316491</v>
       </c>
       <c r="H52" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.28221475096906029</v>
       </c>
       <c r="I52" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.96098208070897E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="20" t="s">
         <v>78</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="17">
-        <f>2*_xlfn.STDEV.S(C39:C50)/COUNT(C39:C50)</f>
-        <v>2.1087007817244052E-2</v>
+        <f>2*_xlfn.STDEV.S(C39:C50)/SQRT(COUNT(C39:C50))</f>
+        <v>7.3047537838137583E-2</v>
       </c>
       <c r="D53" s="17">
-        <f t="shared" ref="D53:I53" si="5">2*_xlfn.STDEV.S(D39:D50)/COUNT(D39:D50)</f>
-        <v>1.5584607076045478E-2</v>
+        <f t="shared" ref="D53:E53" si="7">2*_xlfn.STDEV.S(D39:D50)/SQRT(COUNT(D39:D50))</f>
+        <v>5.3986662543416421E-2</v>
       </c>
       <c r="E53" s="17">
-        <f t="shared" si="5"/>
-        <v>4.9870656645639782E-3</v>
+        <f t="shared" si="7"/>
+        <v>1.7275702223414117E-2</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="17">
-        <f t="shared" si="5"/>
-        <v>3.2398964948748339E-2</v>
+        <f>2*_xlfn.STDEV.S(G39:G50)/SQRT(COUNT(G39:G50))</f>
+        <v>0.11223330680775062</v>
       </c>
       <c r="H53" s="17">
-        <f t="shared" si="5"/>
-        <v>2.9247575326617429E-2</v>
+        <f t="shared" ref="H53:I53" si="8">2*_xlfn.STDEV.S(H39:H50)/SQRT(COUNT(H39:H50))</f>
+        <v>0.10131657292779858</v>
       </c>
       <c r="I53" s="17">
-        <f t="shared" si="5"/>
-        <v>6.0354752381502515E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>2.0907499520600212E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="20" t="s">
         <v>75</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="H55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>0</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>9.0407446521490707E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>2</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>3.2523191705560103E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>7.3646540168298497E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>3.14906670913708E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>5.5512709930258801E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>20</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>6.8278840753294504E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>8.03217169726427E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>22</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>3.8740828316430602E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>0.10369539014665601</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>1.4098924379501601E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>2.7373309337551048E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>5.7099732162515404E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>17</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>0.69114917789727204</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="20" t="s">
         <v>60</v>
       </c>
@@ -3786,59 +3786,59 @@
         <v>0.43118953215410816</v>
       </c>
       <c r="D70" s="17">
-        <f t="shared" ref="D70:I70" si="6">AVERAGE(D57:D68)</f>
+        <f t="shared" ref="D70:I70" si="9">AVERAGE(D57:D68)</f>
         <v>0.60664971797661371</v>
       </c>
       <c r="E70" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.91637380681678626</v>
       </c>
       <c r="F70" s="10"/>
       <c r="G70" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.95911723413134764</v>
       </c>
       <c r="H70" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.57482521919836349</v>
       </c>
       <c r="I70" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>4.3294420861737563E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="20" t="s">
         <v>78</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="17">
-        <f>2*_xlfn.STDEV.S(C57:C68)/COUNT(C57:C68)</f>
-        <v>3.5792961724007706E-2</v>
+        <f>2*_xlfn.STDEV.S(C57:C68)/SQRT(COUNT(C57:C68))</f>
+        <v>0.12399045651869892</v>
       </c>
       <c r="D71" s="17">
-        <f t="shared" ref="D71:I71" si="7">2*_xlfn.STDEV.S(D57:D68)/COUNT(D57:D68)</f>
-        <v>3.3923192506253426E-2</v>
+        <f t="shared" ref="D71:E71" si="10">2*_xlfn.STDEV.S(D57:D68)/SQRT(COUNT(D57:D68))</f>
+        <v>0.11751338595154147</v>
       </c>
       <c r="E71" s="17">
-        <f t="shared" si="7"/>
-        <v>1.1549491277176921E-2</v>
+        <f t="shared" si="10"/>
+        <v>4.0008611387287979E-2</v>
       </c>
       <c r="F71" s="10"/>
       <c r="G71" s="17">
-        <f t="shared" si="7"/>
-        <v>8.5418576653320866E-2</v>
+        <f>2*_xlfn.STDEV.S(G57:G68)/SQRT(COUNT(G57:G68))</f>
+        <v>0.29589862934753691</v>
       </c>
       <c r="H71" s="17">
-        <f t="shared" si="7"/>
-        <v>7.8928420687397902E-2</v>
+        <f t="shared" ref="H71:I71" si="11">2*_xlfn.STDEV.S(H57:H68)/SQRT(COUNT(H57:H68))</f>
+        <v>0.27341606958348724</v>
       </c>
       <c r="I71" s="17">
-        <f t="shared" si="7"/>
-        <v>4.8545264790151622E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v>1.6816573016685422E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="20" t="s">
         <v>76</v>
       </c>
@@ -3851,7 +3851,7 @@
       <c r="H73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>0</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>1</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>1.20725812342692E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>2</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>3.9780870011844598E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>3</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>0.107585210679937</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>1.3085752806885401E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>1.7146158834970501E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>5.4456185796058897E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>6.0180723255630203E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>2.2245608947319698E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>5.0767255412148701E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>24</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>4.0080213975388201E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>6.0180723255630203E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>26</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>7.0246149369644698E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>17</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>0.69114917789727204</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="20" t="s">
         <v>60</v>
       </c>
@@ -4239,60 +4239,66 @@
         <v>0.87004490796468081</v>
       </c>
       <c r="D88" s="17">
-        <f t="shared" ref="D88:I88" si="8">AVERAGE(D75:D86)</f>
+        <f t="shared" ref="D88:I88" si="12">AVERAGE(D75:D86)</f>
         <v>0.89499253530765743</v>
       </c>
       <c r="E88" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.91453888606549505</v>
       </c>
       <c r="F88" s="10"/>
       <c r="G88" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.25462723273879034</v>
       </c>
       <c r="H88" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.15356700164361556</v>
       </c>
       <c r="I88" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.8350700392421945E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="20" t="s">
         <v>78</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="17">
-        <f>2*_xlfn.STDEV.S(C75:C86)/COUNT(C75:C86)</f>
-        <v>1.9664909087356481E-2</v>
+        <f>2*_xlfn.STDEV.S(C75:C86)/SQRT(COUNT(C75:C86))</f>
+        <v>6.81212433310487E-2</v>
       </c>
       <c r="D89" s="17">
-        <f t="shared" ref="D89:I89" si="9">2*_xlfn.STDEV.S(D75:D86)/COUNT(D75:D86)</f>
-        <v>1.5670909683253045E-2</v>
+        <f t="shared" ref="D89:E89" si="13">2*_xlfn.STDEV.S(D75:D86)/SQRT(COUNT(D75:D86))</f>
+        <v>5.4285623544434759E-2</v>
       </c>
       <c r="E89" s="17">
-        <f t="shared" si="9"/>
-        <v>9.2070512761726446E-3</v>
+        <f t="shared" si="13"/>
+        <v>3.1894161196445787E-2</v>
       </c>
       <c r="F89" s="10"/>
       <c r="G89" s="17">
-        <f t="shared" si="9"/>
-        <v>3.2374375099647169E-2</v>
+        <f>2*_xlfn.STDEV.S(G75:G86)/SQRT(COUNT(G75:G86))</f>
+        <v>0.11214812507176328</v>
       </c>
       <c r="H89" s="17">
-        <f t="shared" si="9"/>
-        <v>2.4784125088681681E-2</v>
+        <f t="shared" ref="H89:I89" si="14">2*_xlfn.STDEV.S(H75:H86)/SQRT(COUNT(H75:H86))</f>
+        <v>8.585472774947836E-2</v>
       </c>
       <c r="I89" s="17">
-        <f t="shared" si="9"/>
-        <v>5.0996199305229631E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.7665601637913281E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A73:I73"/>
@@ -4302,12 +4308,6 @@
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A55:I55"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:D15">
     <cfRule type="colorScale" priority="68">
@@ -5031,7 +5031,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C16:I16 C17:E17 G17:I17 C34:I34 C35:I35 C52:E52 G52:I52 C53:I53 C70:I70 C71:I71 C88:E88 G88:I88 C89:I89" formulaRange="1"/>
+    <ignoredError sqref="C16:I16 C34:I34 F35 C52:E52 G52:I52 F53 C70:I70 F71 C88:E88 G88:I88 F89 C17:E17 G17:I17 C35:E35 G35:I35 C53:E53 G53:I53 C71:E71 G71 H71:I71 C89:E89 G89:I89" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>